--- a/data/plc_type.xlsx
+++ b/data/plc_type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\2025\2025 leybold 图论\lbgraph\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1B6A2F-ACF9-4B8E-B9F7-37D063964277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEAF2BFA-2D24-47EF-97B1-DE1E73F1FDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="4990" windowWidth="16080" windowHeight="11440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="2090" windowWidth="22710" windowHeight="9320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="229">
   <si>
     <t>A1,1,DO1.1,RFN_RF on HFN_HN Ein</t>
   </si>
@@ -643,6 +643,99 @@
   </si>
   <si>
     <t>description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>=A02</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>=Q01</t>
+  </si>
+  <si>
+    <t>=P01</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>= Q0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A5</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>A8</t>
+  </si>
+  <si>
+    <t>A9</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>A13</t>
+  </si>
+  <si>
+    <t>=Q15</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>=S02</t>
+  </si>
+  <si>
+    <t>=V01</t>
+  </si>
+  <si>
+    <t>A1.1</t>
+  </si>
+  <si>
+    <t>A2.1</t>
+  </si>
+  <si>
+    <t>A5.1</t>
+  </si>
+  <si>
+    <t>A14</t>
+  </si>
+  <si>
+    <t>Function</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -698,12 +791,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1378,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334D7CDB-E8D4-4E30-9238-4E778D52F7D5}">
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.33203125" style="1" customWidth="1"/>
@@ -1388,913 +1480,1548 @@
     <col min="5" max="5" width="3.5" customWidth="1"/>
     <col min="6" max="6" width="11.08203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="L1" t="s">
+        <v>226</v>
+      </c>
+      <c r="M1" t="s">
+        <v>227</v>
+      </c>
+      <c r="N1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="1" t="str">
-        <f>LEFT(SUBSTITUTE(A1,"=Q01 - A5,",""),FIND(",",SUBSTITUTE(A1,"=Q01 - A5,",""))-1)</f>
+      <c r="B2" s="1" t="str">
+        <f>LEFT(SUBSTITUTE(A2,"=Q01 - A5,",""),FIND(",",SUBSTITUTE(A2,"=Q01 - A5,",""))-1)</f>
         <v>=A02 - A1</v>
       </c>
-      <c r="C1" s="1" t="str">
-        <f>RIGHT(A1,LEN(A1)-FIND(",",A1))</f>
+      <c r="C2" s="1" t="str">
+        <f>RIGHT(A2,LEN(A2)-FIND(",",A2))</f>
         <v>"EL2809"</v>
       </c>
-      <c r="D1" s="1" t="str">
-        <f>MID(C1,2,6)</f>
+      <c r="D2" s="1" t="str">
+        <f>MID(C2,2,6)</f>
         <v>EL2809</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F2" t="s">
         <v>123</v>
-      </c>
-      <c r="G1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="1" t="str">
-        <f t="shared" ref="B2:B46" si="0">LEFT(SUBSTITUTE(A2,"=Q01 - A5,",""),FIND(",",SUBSTITUTE(A2,"=Q01 - A5,",""))-1)</f>
-        <v>=A02 - A2</v>
-      </c>
-      <c r="C2" s="1" t="str">
-        <f t="shared" ref="C2:C46" si="1">RIGHT(A2,LEN(A2)-FIND(",",A2))</f>
-        <v>"EL2809"</v>
-      </c>
-      <c r="D2" s="1" t="str">
-        <f t="shared" ref="D2:D46" si="2">MID(C2,2,6)</f>
-        <v>EL2809</v>
-      </c>
-      <c r="F2" t="s">
-        <v>124</v>
       </c>
       <c r="G2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" t="str">
+        <f>LEFT(F2,4)</f>
+        <v>=A02</v>
+      </c>
+      <c r="J2" t="str">
+        <f>MID(F2,8,20)</f>
+        <v>A1</v>
+      </c>
+      <c r="L2" t="s">
+        <v>199</v>
+      </c>
+      <c r="M2" t="s">
+        <v>200</v>
+      </c>
+      <c r="N2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <f t="shared" ref="B3:B47" si="0">LEFT(SUBSTITUTE(A3,"=Q01 - A5,",""),FIND(",",SUBSTITUTE(A3,"=Q01 - A5,",""))-1)</f>
+        <v>=A02 - A2</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <f t="shared" ref="C3:C47" si="1">RIGHT(A3,LEN(A3)-FIND(",",A3))</f>
+        <v>"EL2809"</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <f t="shared" ref="D3:D47" si="2">MID(C3,2,6)</f>
+        <v>EL2809</v>
+      </c>
+      <c r="F3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I47" si="3">LEFT(F3,4)</f>
+        <v>=A02</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J47" si="4">MID(F3,8,20)</f>
+        <v>A2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>199</v>
+      </c>
+      <c r="M3" t="s">
+        <v>201</v>
+      </c>
+      <c r="N3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B3" s="1" t="str">
+      <c r="B4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=A02 - A3</v>
       </c>
-      <c r="C3" s="1" t="str">
+      <c r="C4" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1809"</v>
       </c>
-      <c r="D3" s="1" t="str">
+      <c r="D4" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1809</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
         <v>125</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="I4" t="str">
+        <f t="shared" si="3"/>
+        <v>=A02</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="4"/>
+        <v>A3</v>
+      </c>
+      <c r="L4" t="s">
+        <v>199</v>
+      </c>
+      <c r="M4" t="s">
+        <v>202</v>
+      </c>
+      <c r="N4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="1" t="str">
+      <c r="B5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=A02 - A4</v>
       </c>
-      <c r="C4" s="1" t="str">
+      <c r="C5" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3204"</v>
       </c>
-      <c r="D4" s="1" t="str">
+      <c r="D5" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3204</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>126</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="I5" t="str">
+        <f t="shared" si="3"/>
+        <v>=A02</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="4"/>
+        <v>A4</v>
+      </c>
+      <c r="L5" t="s">
+        <v>199</v>
+      </c>
+      <c r="M5" t="s">
+        <v>203</v>
+      </c>
+      <c r="N5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="1" t="str">
+      <c r="B6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=A02 - A5</v>
       </c>
-      <c r="C5" s="1" t="str">
+      <c r="C6" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3403 - 0010 3AC/5A"</v>
       </c>
-      <c r="D5" s="1" t="str">
+      <c r="D6" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3403</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
         <v>127</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G6" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="I6" t="str">
+        <f t="shared" si="3"/>
+        <v>=A02</v>
+      </c>
+      <c r="J6" t="str">
+        <f t="shared" si="4"/>
+        <v>A5</v>
+      </c>
+      <c r="L6" t="s">
+        <v>199</v>
+      </c>
+      <c r="M6" t="s">
+        <v>204</v>
+      </c>
+      <c r="N6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B6" s="1" t="str">
+      <c r="B7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A1</v>
       </c>
-      <c r="C6" s="1" t="str">
+      <c r="C7" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1859"</v>
       </c>
-      <c r="D6" s="1" t="str">
+      <c r="D7" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1859</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>128</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="I7" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J7" t="str">
+        <f t="shared" si="4"/>
+        <v>A1</v>
+      </c>
+      <c r="L7" t="s">
+        <v>205</v>
+      </c>
+      <c r="M7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B7" s="1" t="str">
+      <c r="B8" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A2</v>
       </c>
-      <c r="C7" s="1" t="str">
+      <c r="C8" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4004"</v>
       </c>
-      <c r="D7" s="1" t="str">
+      <c r="D8" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4004</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>129</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G8" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="I8" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="4"/>
+        <v>A2</v>
+      </c>
+      <c r="L8" t="s">
+        <v>205</v>
+      </c>
+      <c r="M8" t="s">
+        <v>201</v>
+      </c>
+      <c r="N8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B8" s="1" t="str">
+      <c r="B9" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A3</v>
       </c>
-      <c r="C8" s="1" t="str">
+      <c r="C9" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3064, 4AI"</v>
       </c>
-      <c r="D8" s="1" t="str">
+      <c r="D9" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3064</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F9" t="s">
         <v>130</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G9" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="I9" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="4"/>
+        <v>A3</v>
+      </c>
+      <c r="L9" t="s">
+        <v>205</v>
+      </c>
+      <c r="M9" t="s">
+        <v>202</v>
+      </c>
+      <c r="N9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B9" s="1" t="str">
+      <c r="B10" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A4</v>
       </c>
-      <c r="C9" s="1" t="str">
+      <c r="C10" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1859"</v>
       </c>
-      <c r="D9" s="1" t="str">
+      <c r="D10" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1859</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>131</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G10" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="I10" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="4"/>
+        <v>A4</v>
+      </c>
+      <c r="L10" t="s">
+        <v>205</v>
+      </c>
+      <c r="M10" t="s">
+        <v>203</v>
+      </c>
+      <c r="N10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="1" t="str">
+      <c r="B11" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=P01 - T1</v>
       </c>
-      <c r="C10" s="1" t="str">
+      <c r="C11" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL9400"</v>
       </c>
-      <c r="D10" s="1" t="str">
+      <c r="D11" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL9400</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F11" t="s">
         <v>132</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G11" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="I11" t="str">
+        <f t="shared" si="3"/>
+        <v>=P01</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="4"/>
+        <v>T1</v>
+      </c>
+      <c r="L11" t="s">
+        <v>206</v>
+      </c>
+      <c r="M11" t="s">
+        <v>207</v>
+      </c>
+      <c r="N11" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B11" s="1" t="str">
+      <c r="B12" s="1" t="str">
         <f t="shared" si="0"/>
         <v>= Q01 - A5</v>
       </c>
-      <c r="C11" s="1" t="str">
+      <c r="C12" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4132, 2AO, 16Bit"</v>
       </c>
-      <c r="D11" s="1" t="str">
+      <c r="D12" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4132</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>176</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G12" t="s">
         <v>170</v>
       </c>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="H12" s="1"/>
+      <c r="I12" t="str">
+        <f t="shared" si="3"/>
+        <v>= Q0</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="4"/>
+        <v xml:space="preserve"> A5</v>
+      </c>
+      <c r="L12" t="s">
+        <v>208</v>
+      </c>
+      <c r="M12" t="s">
+        <v>209</v>
+      </c>
+      <c r="N12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="B12" s="1" t="str">
+      <c r="B13" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A6</v>
       </c>
-      <c r="C12" s="1" t="str">
+      <c r="C13" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL8601 - 8411"</v>
       </c>
-      <c r="D12" s="1" t="str">
+      <c r="D13" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL8601</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F13" t="s">
         <v>133</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G13" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="I13" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="4"/>
+        <v>A6</v>
+      </c>
+      <c r="L13" t="s">
+        <v>205</v>
+      </c>
+      <c r="M13" t="s">
+        <v>210</v>
+      </c>
+      <c r="N13" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B13" s="1" t="str">
+      <c r="B14" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A7</v>
       </c>
-      <c r="C13" s="1" t="str">
+      <c r="C14" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1859"</v>
       </c>
-      <c r="D13" s="1" t="str">
+      <c r="D14" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1859</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F14" t="s">
         <v>134</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G14" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="I14" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" si="4"/>
+        <v>A7</v>
+      </c>
+      <c r="L14" t="s">
+        <v>205</v>
+      </c>
+      <c r="M14" t="s">
+        <v>211</v>
+      </c>
+      <c r="N14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="1" t="str">
+      <c r="B15" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A8</v>
       </c>
-      <c r="C14" s="1" t="str">
+      <c r="C15" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4132, 2AO, 16Bit"</v>
       </c>
-      <c r="D14" s="1" t="str">
+      <c r="D15" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4132</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F15" t="s">
         <v>135</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G15" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="I15" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="4"/>
+        <v>A8</v>
+      </c>
+      <c r="L15" t="s">
+        <v>205</v>
+      </c>
+      <c r="M15" t="s">
+        <v>212</v>
+      </c>
+      <c r="N15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B15" s="1" t="str">
+      <c r="B16" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A9</v>
       </c>
-      <c r="C15" s="1" t="str">
+      <c r="C16" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL8601 - 8411"</v>
       </c>
-      <c r="D15" s="1" t="str">
+      <c r="D16" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL8601</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F16" t="s">
         <v>136</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G16" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="I16" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="4"/>
+        <v>A9</v>
+      </c>
+      <c r="L16" t="s">
+        <v>205</v>
+      </c>
+      <c r="M16" t="s">
+        <v>213</v>
+      </c>
+      <c r="N16" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="1" t="str">
+      <c r="B17" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A10</v>
       </c>
-      <c r="C16" s="1" t="str">
+      <c r="C17" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4004, 4AO"</v>
       </c>
-      <c r="D16" s="1" t="str">
+      <c r="D17" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4004</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F17" t="s">
         <v>137</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G17" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="I17" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="4"/>
+        <v>A10</v>
+      </c>
+      <c r="L17" t="s">
+        <v>205</v>
+      </c>
+      <c r="M17" t="s">
+        <v>214</v>
+      </c>
+      <c r="N17" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B17" s="1" t="str">
+      <c r="B18" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A11</v>
       </c>
-      <c r="C17" s="1" t="str">
+      <c r="C18" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3064, 4AI"</v>
       </c>
-      <c r="D17" s="1" t="str">
+      <c r="D18" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3064</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F18" t="s">
         <v>138</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G18" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="I18" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="4"/>
+        <v>A11</v>
+      </c>
+      <c r="L18" t="s">
+        <v>205</v>
+      </c>
+      <c r="M18" t="s">
+        <v>215</v>
+      </c>
+      <c r="N18" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="1" t="str">
+      <c r="B19" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A12</v>
       </c>
-      <c r="C18" s="1" t="str">
+      <c r="C19" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3162, 2AI"</v>
       </c>
-      <c r="D18" s="1" t="str">
+      <c r="D19" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3162</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>139</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="I19" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="4"/>
+        <v>A12</v>
+      </c>
+      <c r="L19" t="s">
+        <v>205</v>
+      </c>
+      <c r="M19" t="s">
+        <v>216</v>
+      </c>
+      <c r="N19" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B19" s="1" t="str">
+      <c r="B20" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q01 - A13</v>
       </c>
-      <c r="C19" s="1" t="str">
+      <c r="C20" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1004, 4DI (3.0ms)"</v>
       </c>
-      <c r="D19" s="1" t="str">
+      <c r="D20" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1004</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F20" t="s">
         <v>140</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G20" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="I20" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q01</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="4"/>
+        <v>A13</v>
+      </c>
+      <c r="L20" t="s">
+        <v>205</v>
+      </c>
+      <c r="M20" t="s">
+        <v>217</v>
+      </c>
+      <c r="N20" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="1" t="str">
+      <c r="B21" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A1</v>
       </c>
-      <c r="C20" s="1" t="str">
+      <c r="C21" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL2809, 16DO"</v>
       </c>
-      <c r="D20" s="1" t="str">
+      <c r="D21" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL2809</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F21" t="s">
         <v>141</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G21" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="I21" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="4"/>
+        <v>A1</v>
+      </c>
+      <c r="L21" t="s">
+        <v>218</v>
+      </c>
+      <c r="M21" t="s">
+        <v>200</v>
+      </c>
+      <c r="N21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="1" t="str">
+      <c r="B22" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A2</v>
       </c>
-      <c r="C21" s="1" t="str">
+      <c r="C22" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1809, 16DI"</v>
       </c>
-      <c r="D21" s="1" t="str">
+      <c r="D22" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1809</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>142</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G22" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="I22" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J22" t="str">
+        <f t="shared" si="4"/>
+        <v>A2</v>
+      </c>
+      <c r="L22" t="s">
+        <v>218</v>
+      </c>
+      <c r="M22" t="s">
+        <v>201</v>
+      </c>
+      <c r="N22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="1" t="str">
+      <c r="B23" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A3</v>
       </c>
-      <c r="C22" s="1" t="str">
+      <c r="C23" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4004, 4AO"</v>
       </c>
-      <c r="D22" s="1" t="str">
+      <c r="D23" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4004</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F23" t="s">
         <v>143</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G23" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="I23" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="4"/>
+        <v>A3</v>
+      </c>
+      <c r="L23" t="s">
+        <v>218</v>
+      </c>
+      <c r="M23" t="s">
+        <v>202</v>
+      </c>
+      <c r="N23" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="1" t="str">
+      <c r="B24" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A4</v>
       </c>
-      <c r="C23" s="1" t="str">
+      <c r="C24" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3064, 4AI"</v>
       </c>
-      <c r="D23" s="1" t="str">
+      <c r="D24" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3064</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24" t="s">
         <v>144</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G24" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="I24" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J24" t="str">
+        <f t="shared" si="4"/>
+        <v>A4</v>
+      </c>
+      <c r="L24" t="s">
+        <v>218</v>
+      </c>
+      <c r="M24" t="s">
+        <v>203</v>
+      </c>
+      <c r="N24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="1" t="str">
+      <c r="B25" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A5</v>
       </c>
-      <c r="C24" s="1" t="str">
+      <c r="C25" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4004, 4AO"</v>
       </c>
-      <c r="D24" s="1" t="str">
+      <c r="D25" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4004</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F25" t="s">
         <v>145</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G25" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="I25" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J25" t="str">
+        <f t="shared" si="4"/>
+        <v>A5</v>
+      </c>
+      <c r="L25" t="s">
+        <v>218</v>
+      </c>
+      <c r="M25" t="s">
+        <v>204</v>
+      </c>
+      <c r="N25" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B25" s="1" t="str">
+      <c r="B26" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A6</v>
       </c>
-      <c r="C25" s="1" t="str">
+      <c r="C26" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3064, 4AI"</v>
       </c>
-      <c r="D25" s="1" t="str">
+      <c r="D26" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3064</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F26" t="s">
         <v>146</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G26" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="I26" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="4"/>
+        <v>A6</v>
+      </c>
+      <c r="L26" t="s">
+        <v>218</v>
+      </c>
+      <c r="M26" t="s">
+        <v>210</v>
+      </c>
+      <c r="N26" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="1" t="str">
+      <c r="B27" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=P01 - T2</v>
       </c>
-      <c r="C26" s="1" t="str">
+      <c r="C27" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL9100"</v>
       </c>
-      <c r="D26" s="1" t="str">
+      <c r="D27" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL9100</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F27" t="s">
         <v>147</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G27" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="I27" t="str">
+        <f t="shared" si="3"/>
+        <v>=P01</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="4"/>
+        <v>T2</v>
+      </c>
+      <c r="L27" t="s">
+        <v>206</v>
+      </c>
+      <c r="M27" t="s">
+        <v>219</v>
+      </c>
+      <c r="N27" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="1" t="str">
+      <c r="B28" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A7</v>
       </c>
-      <c r="C27" s="1" t="str">
+      <c r="C28" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4004, 4AO"</v>
       </c>
-      <c r="D27" s="1" t="str">
+      <c r="D28" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4004</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>148</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G28" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="I28" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="4"/>
+        <v>A7</v>
+      </c>
+      <c r="L28" t="s">
+        <v>218</v>
+      </c>
+      <c r="M28" t="s">
+        <v>211</v>
+      </c>
+      <c r="N28" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B28" s="1" t="str">
+      <c r="B29" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A8</v>
       </c>
-      <c r="C28" s="1" t="str">
+      <c r="C29" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3064, 4AI"</v>
       </c>
-      <c r="D28" s="1" t="str">
+      <c r="D29" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3064</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F29" t="s">
         <v>149</v>
       </c>
-      <c r="G28" t="s">
+      <c r="G29" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="I29" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="4"/>
+        <v>A8</v>
+      </c>
+      <c r="L29" t="s">
+        <v>218</v>
+      </c>
+      <c r="M29" t="s">
+        <v>212</v>
+      </c>
+      <c r="N29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B29" s="1" t="str">
+      <c r="B30" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A9</v>
       </c>
-      <c r="C29" s="1" t="str">
+      <c r="C30" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1859"</v>
       </c>
-      <c r="D29" s="1" t="str">
+      <c r="D30" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1859</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>150</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G30" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="I30" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="4"/>
+        <v>A9</v>
+      </c>
+      <c r="L30" t="s">
+        <v>218</v>
+      </c>
+      <c r="M30" t="s">
+        <v>213</v>
+      </c>
+      <c r="N30" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="1" t="str">
+      <c r="B31" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A10</v>
       </c>
-      <c r="C30" s="1" t="str">
+      <c r="C31" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL4004, 4AO"</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D31" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL4004</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F31" t="s">
         <v>151</v>
       </c>
-      <c r="G30" t="s">
+      <c r="G31" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+      <c r="I31" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="4"/>
+        <v>A10</v>
+      </c>
+      <c r="L31" t="s">
+        <v>218</v>
+      </c>
+      <c r="M31" t="s">
+        <v>214</v>
+      </c>
+      <c r="N31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B31" s="1" t="str">
+      <c r="B32" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=Q15 - A11</v>
       </c>
-      <c r="C31" s="1" t="str">
+      <c r="C32" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3064, 4AI"</v>
       </c>
-      <c r="D31" s="1" t="str">
+      <c r="D32" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3064</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F32" t="s">
         <v>152</v>
-      </c>
-      <c r="G31" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>=Q15 - A12</v>
-      </c>
-      <c r="C32" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>"EL3064, 4AI"</v>
-      </c>
-      <c r="D32" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EL3064</v>
-      </c>
-      <c r="F32" t="s">
-        <v>153</v>
       </c>
       <c r="G32" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I32" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" si="4"/>
+        <v>A11</v>
+      </c>
+      <c r="L32" t="s">
+        <v>218</v>
+      </c>
+      <c r="M32" t="s">
+        <v>215</v>
+      </c>
+      <c r="N32" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>=Q15 - A12</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>"EL3064, 4AI"</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EL3064</v>
+      </c>
+      <c r="F33" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" t="s">
+        <v>169</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="3"/>
+        <v>=Q15</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="4"/>
+        <v>A12</v>
+      </c>
+      <c r="L33" t="s">
+        <v>218</v>
+      </c>
+      <c r="M33" t="s">
+        <v>216</v>
+      </c>
+      <c r="N33" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="1" t="str">
+      <c r="B34" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=S02 - A1</v>
       </c>
-      <c r="C33" s="1" t="str">
+      <c r="C34" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1859"</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D34" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1859</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F34" t="s">
         <v>154</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G34" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="I34" t="str">
+        <f t="shared" si="3"/>
+        <v>=S02</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="4"/>
+        <v>A1</v>
+      </c>
+      <c r="L34" t="s">
+        <v>220</v>
+      </c>
+      <c r="M34" t="s">
+        <v>200</v>
+      </c>
+      <c r="N34" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B34" s="1" t="str">
+      <c r="B35" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A1</v>
       </c>
-      <c r="C34" s="1" t="str">
+      <c r="C35" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL2809, 16DO"</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL2809</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>155</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G35" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="I35" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="4"/>
+        <v>A1</v>
+      </c>
+      <c r="L35" t="s">
+        <v>221</v>
+      </c>
+      <c r="M35" t="s">
+        <v>200</v>
+      </c>
+      <c r="N35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B35" s="1" t="str">
+      <c r="B36" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A1.1</v>
       </c>
-      <c r="C35" s="1" t="str">
+      <c r="C36" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL9100"</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D36" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL9100</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F36" t="s">
         <v>156</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G36" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="I36" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="4"/>
+        <v>A1.1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>221</v>
+      </c>
+      <c r="M36" t="s">
+        <v>222</v>
+      </c>
+      <c r="N36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B36" s="1" t="str">
+      <c r="B37" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A2</v>
       </c>
-      <c r="C36" s="1" t="str">
+      <c r="C37" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL2809, 16DO"</v>
       </c>
-      <c r="D36" s="1" t="str">
+      <c r="D37" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL2809</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F37" t="s">
         <v>157</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G37" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="I37" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J37" t="str">
+        <f t="shared" si="4"/>
+        <v>A2</v>
+      </c>
+      <c r="L37" t="s">
+        <v>221</v>
+      </c>
+      <c r="M37" t="s">
+        <v>201</v>
+      </c>
+      <c r="N37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="1" t="str">
+      <c r="B38" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A2.1</v>
       </c>
-      <c r="C37" s="1" t="str">
+      <c r="C38" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL9100"</v>
       </c>
-      <c r="D37" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL9100</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F38" t="s">
         <v>158</v>
       </c>
-      <c r="G37" t="s">
+      <c r="G38" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="I38" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J38" t="str">
+        <f t="shared" si="4"/>
+        <v>A2.1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>221</v>
+      </c>
+      <c r="M38" t="s">
+        <v>223</v>
+      </c>
+      <c r="N38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B38" s="1" t="str">
+      <c r="B39" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A3</v>
       </c>
-      <c r="C38" s="1" t="str">
+      <c r="C39" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL1809, 16DI"</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL1809</v>
       </c>
-      <c r="F38" t="s">
+      <c r="F39" t="s">
         <v>159</v>
-      </c>
-      <c r="G38" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>=V01 - A4</v>
-      </c>
-      <c r="C39" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>"EL1809, 16DI"</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EL1809</v>
-      </c>
-      <c r="F39" t="s">
-        <v>160</v>
       </c>
       <c r="G39" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I39" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J39" t="str">
+        <f t="shared" si="4"/>
+        <v>A3</v>
+      </c>
+      <c r="L39" t="s">
+        <v>221</v>
+      </c>
+      <c r="M39" t="s">
+        <v>202</v>
+      </c>
+      <c r="N39" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B40" s="1" t="str">
         <f t="shared" si="0"/>
-        <v>=V01 - A5</v>
+        <v>=V01 - A4</v>
       </c>
       <c r="C40" s="1" t="str">
         <f t="shared" si="1"/>
@@ -2305,147 +3032,306 @@
         <v>EL1809</v>
       </c>
       <c r="F40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G40" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I40" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J40" t="str">
+        <f t="shared" si="4"/>
+        <v>A4</v>
+      </c>
+      <c r="L40" t="s">
+        <v>221</v>
+      </c>
+      <c r="M40" t="s">
+        <v>203</v>
+      </c>
+      <c r="N40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B41" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>=V01 - A5</v>
+      </c>
+      <c r="C41" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>"EL1809, 16DI"</v>
+      </c>
+      <c r="D41" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EL1809</v>
+      </c>
+      <c r="F41" t="s">
+        <v>161</v>
+      </c>
+      <c r="G41" t="s">
+        <v>77</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J41" t="str">
+        <f t="shared" si="4"/>
+        <v>A5</v>
+      </c>
+      <c r="L41" t="s">
+        <v>221</v>
+      </c>
+      <c r="M41" t="s">
+        <v>204</v>
+      </c>
+      <c r="N41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B41" s="1" t="str">
+      <c r="B42" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A5.1</v>
       </c>
-      <c r="C41" s="1" t="str">
+      <c r="C42" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL9100"</v>
       </c>
-      <c r="D41" s="1" t="str">
+      <c r="D42" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL9100</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F42" t="s">
         <v>162</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G42" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
+      <c r="I42" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J42" t="str">
+        <f t="shared" si="4"/>
+        <v>A5.1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>221</v>
+      </c>
+      <c r="M42" t="s">
+        <v>224</v>
+      </c>
+      <c r="N42" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B42" s="1" t="str">
+      <c r="B43" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A6</v>
       </c>
-      <c r="C42" s="1" t="str">
+      <c r="C43" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3064, 4AI"</v>
       </c>
-      <c r="D42" s="1" t="str">
+      <c r="D43" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3064</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F43" t="s">
         <v>163</v>
-      </c>
-      <c r="G42" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B43" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v>=V01 - A7</v>
-      </c>
-      <c r="C43" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v>"EL3064, 4AI"</v>
-      </c>
-      <c r="D43" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v>EL3064</v>
-      </c>
-      <c r="F43" t="s">
-        <v>164</v>
       </c>
       <c r="G43" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="I43" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J43" t="str">
+        <f t="shared" si="4"/>
+        <v>A6</v>
+      </c>
+      <c r="L43" t="s">
+        <v>221</v>
+      </c>
+      <c r="M43" t="s">
+        <v>210</v>
+      </c>
+      <c r="N43" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>=V01 - A7</v>
+      </c>
+      <c r="C44" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>"EL3064, 4AI"</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v>EL3064</v>
+      </c>
+      <c r="F44" t="s">
+        <v>164</v>
+      </c>
+      <c r="G44" t="s">
+        <v>169</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J44" t="str">
+        <f t="shared" si="4"/>
+        <v>A7</v>
+      </c>
+      <c r="L44" t="s">
+        <v>221</v>
+      </c>
+      <c r="M44" t="s">
+        <v>211</v>
+      </c>
+      <c r="N44" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="1" t="str">
+      <c r="B45" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A8</v>
       </c>
-      <c r="C44" s="1" t="str">
+      <c r="C45" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL3314, 4XTC"</v>
       </c>
-      <c r="D44" s="1" t="str">
+      <c r="D45" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL3314</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F45" t="s">
         <v>165</v>
       </c>
-      <c r="G44" t="s">
+      <c r="G45" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
+      <c r="I45" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J45" t="str">
+        <f t="shared" si="4"/>
+        <v>A8</v>
+      </c>
+      <c r="L45" t="s">
+        <v>221</v>
+      </c>
+      <c r="M45" t="s">
+        <v>212</v>
+      </c>
+      <c r="N45" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B45" s="1" t="str">
+      <c r="B46" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A13</v>
       </c>
-      <c r="C45" s="1" t="str">
+      <c r="C46" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"Profibus Master\nProfibus master"</v>
       </c>
-      <c r="D45" s="1" t="str">
+      <c r="D46" s="1" t="str">
         <f t="shared" si="2"/>
         <v>Profib</v>
       </c>
-      <c r="F45" t="s">
+      <c r="F46" t="s">
         <v>166</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G46" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
+      <c r="I46" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J46" t="str">
+        <f t="shared" si="4"/>
+        <v>A13</v>
+      </c>
+      <c r="L46" t="s">
+        <v>221</v>
+      </c>
+      <c r="M46" t="s">
+        <v>217</v>
+      </c>
+      <c r="N46" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="1" t="str">
+      <c r="B47" s="1" t="str">
         <f t="shared" si="0"/>
         <v>=V01 - A14</v>
       </c>
-      <c r="C46" s="1" t="str">
+      <c r="C47" s="1" t="str">
         <f t="shared" si="1"/>
         <v>"EL9011"</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D47" s="1" t="str">
         <f t="shared" si="2"/>
         <v>EL9011</v>
       </c>
-      <c r="F46" t="s">
+      <c r="F47" t="s">
         <v>167</v>
       </c>
-      <c r="G46" t="s">
+      <c r="G47" t="s">
+        <v>81</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="3"/>
+        <v>=V01</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="4"/>
+        <v>A14</v>
+      </c>
+      <c r="L47" t="s">
+        <v>221</v>
+      </c>
+      <c r="M47" t="s">
+        <v>225</v>
+      </c>
+      <c r="N47" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2460,141 +3346,140 @@
   <dimension ref="B1:D12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="13.83203125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="40.58203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" style="4" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="4"/>
+    <col min="1" max="3" width="13.83203125" customWidth="1"/>
+    <col min="4" max="4" width="40.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
+      <c r="B1" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="2" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>78</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>8</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>169</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>4</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>6</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>171</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9">
         <v>4</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>172</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10">
         <v>2</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>173</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11">
         <v>4</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12">
         <v>4</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" t="s">
         <v>193</v>
       </c>
     </row>
